--- a/MDC/MDC_Precio_t.xlsx
+++ b/MDC/MDC_Precio_t.xlsx
@@ -1297,7 +1297,7 @@
     <t>06410211.01</t>
   </si>
   <si>
-    <t>Yip's</t>
+    <t>Supermercado 1</t>
   </si>
   <si>
     <t>Precio</t>
@@ -1720,7 +1720,7 @@
     <t>62.4145</t>
   </si>
   <si>
-    <t>La Colonia # 1</t>
+    <t>Supermercado 2</t>
   </si>
   <si>
     <t>58.40515408</t>
@@ -2149,7 +2149,7 @@
     <t>55.062</t>
   </si>
   <si>
-    <t>Los almendros</t>
+    <t>Mercadito 1</t>
   </si>
   <si>
     <t>Mercadito Precio t</t>
@@ -2179,7 +2179,7 @@
     <t>10.105</t>
   </si>
   <si>
-    <t>5 estrellas</t>
+    <t>Mercadito 2</t>
   </si>
   <si>
     <t>12.8205</t>
